--- a/BWI/bestwine_output/bestwine_French Polynesia.xlsx
+++ b/BWI/bestwine_output/bestwine_French Polynesia.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA17"/>
+  <dimension ref="A1:AA20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2283,6 +2283,297 @@
       <c r="Z17" s="3" t="inlineStr"/>
       <c r="AA17" s="3" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Societe De Distribution Polynesienne Sa</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Societe De Distribution Polynesienne Sa</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>5242</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>French Polynesia</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Pape'ete</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Windward Islands</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Z.i. De Papeava, Entrepot No. 3 &amp; 4, Port Autonome De Papeete</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>98714</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pavillondesvins.pf, https://www.sodispo.pf</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>cedric@sodispo.pf</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>+689 40 50 58 88</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr"/>
+      <c r="V18" s="2" t="inlineStr"/>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>Mathilde Sétif</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>Marketing &amp; Sales Administration Manager</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr"/>
+      <c r="Z18" s="2" t="inlineStr"/>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mathilde-s%c3%a9tif-66397732/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Societe De Distribution Polynesienne Sa</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Societe De Distribution Polynesienne Sa</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>5242</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>French Polynesia</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Pape'ete</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Windward Islands</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Z.i. De Papeava, Entrepot No. 3 &amp; 4, Port Autonome De Papeete</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>98714</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pavillondesvins.pf, https://www.sodispo.pf</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>cedric@sodispo.pf</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>+689 40 50 58 88</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr"/>
+      <c r="V19" s="2" t="inlineStr"/>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>Clet Wong</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr"/>
+      <c r="Z19" s="2" t="inlineStr"/>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/clet-wong-a2a3b711/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Societe De Distribution Polynesienne Sa</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Societe De Distribution Polynesienne Sa</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>5242</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>French Polynesia</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Pape'ete</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Windward Islands</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Z.i. De Papeava, Entrepot No. 3 &amp; 4, Port Autonome De Papeete</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>98714</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pavillondesvins.pf, https://www.sodispo.pf</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>cedric@sodispo.pf</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>+689 40 50 58 88</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr"/>
+      <c r="V20" s="2" t="inlineStr"/>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>Cedric Molina</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>Manager of Sales</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr"/>
+      <c r="Z20" s="2" t="inlineStr"/>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/cedric-molina-a51569129/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_French Polynesia.xlsx
+++ b/BWI/bestwine_output/bestwine_French Polynesia.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA20"/>
+  <dimension ref="A1:AA23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2574,6 +2574,297 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Societe De Distribution Polynesienne Sa</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Societe De Distribution Polynesienne Sa</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>5242</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>French Polynesia</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Pape'ete</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Windward Islands</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Z.i. De Papeava, Entrepot No. 3 &amp; 4, Port Autonome De Papeete</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>98714</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pavillondesvins.pf, https://www.sodispo.pf</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>cedric@sodispo.pf</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>+689 40 50 58 88</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr"/>
+      <c r="V21" s="2" t="inlineStr"/>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>Mathilde Sétif</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>Marketing &amp; Sales Administration Manager</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr"/>
+      <c r="Z21" s="2" t="inlineStr"/>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mathilde-s%c3%a9tif-66397732/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Societe De Distribution Polynesienne Sa</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Societe De Distribution Polynesienne Sa</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>5242</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>French Polynesia</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Pape'ete</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Windward Islands</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Z.i. De Papeava, Entrepot No. 3 &amp; 4, Port Autonome De Papeete</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>98714</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pavillondesvins.pf, https://www.sodispo.pf</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>cedric@sodispo.pf</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>+689 40 50 58 88</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr"/>
+      <c r="V22" s="2" t="inlineStr"/>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>Clet Wong</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr"/>
+      <c r="Z22" s="2" t="inlineStr"/>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/clet-wong-a2a3b711/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Societe De Distribution Polynesienne Sa</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Societe De Distribution Polynesienne Sa</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>5242</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>French Polynesia</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Pape'ete</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Windward Islands</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Z.i. De Papeava, Entrepot No. 3 &amp; 4, Port Autonome De Papeete</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>98714</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pavillondesvins.pf, https://www.sodispo.pf</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>cedric@sodispo.pf</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>+689 40 50 58 88</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr"/>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>Cedric Molina</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>Manager of Sales</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr"/>
+      <c r="Z23" s="2" t="inlineStr"/>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/cedric-molina-a51569129/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_French Polynesia.xlsx
+++ b/BWI/bestwine_output/bestwine_French Polynesia.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA23"/>
+  <dimension ref="A1:AA26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2865,6 +2865,297 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Societe De Distribution Polynesienne Sa</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Societe De Distribution Polynesienne Sa</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>5242</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>French Polynesia</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Pape'ete</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Windward Islands</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Z.i. De Papeava, Entrepot No. 3 &amp; 4, Port Autonome De Papeete</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>98714</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pavillondesvins.pf, https://www.sodispo.pf</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>cedric@sodispo.pf</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>+689 40 50 58 88</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr"/>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>Mathilde Sétif</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>Marketing &amp; Sales Administration Manager</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr"/>
+      <c r="Z24" s="2" t="inlineStr"/>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mathilde-s%c3%a9tif-66397732/</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Societe De Distribution Polynesienne Sa</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Societe De Distribution Polynesienne Sa</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>5242</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>French Polynesia</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Pape'ete</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Windward Islands</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Z.i. De Papeava, Entrepot No. 3 &amp; 4, Port Autonome De Papeete</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>98714</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pavillondesvins.pf, https://www.sodispo.pf</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>cedric@sodispo.pf</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>+689 40 50 58 88</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr"/>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>Clet Wong</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr"/>
+      <c r="Z25" s="2" t="inlineStr"/>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/clet-wong-a2a3b711/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Societe De Distribution Polynesienne Sa</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Societe De Distribution Polynesienne Sa</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>5242</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>French Polynesia</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Pape'ete</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Windward Islands</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Z.i. De Papeava, Entrepot No. 3 &amp; 4, Port Autonome De Papeete</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>98714</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pavillondesvins.pf, https://www.sodispo.pf</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>cedric@sodispo.pf</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>+689 40 50 58 88</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr"/>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>Cedric Molina</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>Manager of Sales</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr"/>
+      <c r="Z26" s="2" t="inlineStr"/>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/cedric-molina-a51569129/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_French Polynesia.xlsx
+++ b/BWI/bestwine_output/bestwine_French Polynesia.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA26"/>
+  <dimension ref="A1:AA29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3156,6 +3156,297 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Societe De Distribution Polynesienne Sa</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Societe De Distribution Polynesienne Sa</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>5242</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>French Polynesia</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Pape'ete</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Windward Islands</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Z.i. De Papeava, Entrepot No. 3 &amp; 4, Port Autonome De Papeete</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>98714</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pavillondesvins.pf, https://www.sodispo.pf</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>cedric@sodispo.pf</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>+689 40 50 58 88</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr"/>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>Cedric Molina</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>Manager of Sales</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr"/>
+      <c r="Z27" s="2" t="inlineStr"/>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/cedric-molina-a51569129/</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Societe De Distribution Polynesienne Sa</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Societe De Distribution Polynesienne Sa</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>5242</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>French Polynesia</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Pape'ete</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Windward Islands</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Z.i. De Papeava, Entrepot No. 3 &amp; 4, Port Autonome De Papeete</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>98714</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pavillondesvins.pf, https://www.sodispo.pf</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>cedric@sodispo.pf</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>+689 40 50 58 88</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr"/>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>Mathilde Sétif</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>Marketing &amp; Sales Administration Manager</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr"/>
+      <c r="Z28" s="2" t="inlineStr"/>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mathilde-s%c3%a9tif-66397732/</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Societe De Distribution Polynesienne Sa</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Societe De Distribution Polynesienne Sa</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>5242</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>French Polynesia</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Pape'ete</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Windward Islands</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Z.i. De Papeava, Entrepot No. 3 &amp; 4, Port Autonome De Papeete</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>98714</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pavillondesvins.pf, https://www.sodispo.pf</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>cedric@sodispo.pf</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>+689 40 50 58 88</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr"/>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>Clet Wong</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr"/>
+      <c r="Z29" s="2" t="inlineStr"/>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/clet-wong-a2a3b711/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_French Polynesia.xlsx
+++ b/BWI/bestwine_output/bestwine_French Polynesia.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA29"/>
+  <dimension ref="A1:AA31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3447,6 +3447,208 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Carrefour Polynésie</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Carrefour Polynésie</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>90104</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>French Polynesia</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Faaa</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Îles du Vent</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Immeuble Mana Nui</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>98 704</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>https://carrefour.pf</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>sages@sages.pf</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>+689 40 46 08 08</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr"/>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/carrefourpolynesie</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/carrefourpolynesie</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/carrefourtahiti2011</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>Eric Corlier</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>Director Of Development</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr"/>
+      <c r="Z30" s="2" t="inlineStr"/>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/eric-corlier-b8644840/</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Carrefour Polynésie</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Carrefour Polynésie</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>90104</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>French Polynesia</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Faaa</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Îles du Vent</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Immeuble Mana Nui</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>98 704</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>https://carrefour.pf</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>sages@sages.pf</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>+689 40 46 08 08</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr"/>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/carrefourpolynesie</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/carrefourpolynesie</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/carrefourtahiti2011</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>Jocelyn Bonneau</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr"/>
+      <c r="Z31" s="2" t="inlineStr"/>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jocelyn-bonneau-aa75341b0/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_French Polynesia.xlsx
+++ b/BWI/bestwine_output/bestwine_French Polynesia.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA31"/>
+  <dimension ref="A1:AA33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3649,6 +3649,208 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Carrefour Polynésie</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Carrefour Polynésie</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>90104</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>French Polynesia</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Faaa</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Îles du Vent</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Immeuble Mana Nui</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>98 704</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>https://carrefour.pf</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>sages@sages.pf</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>+689 40 46 08 08</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr"/>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/carrefourpolynesie</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/carrefourpolynesie</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/carrefourtahiti2011</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>Eric Corlier</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>Director Of Development</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr"/>
+      <c r="Z32" s="2" t="inlineStr"/>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/eric-corlier-b8644840/</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Carrefour Polynésie</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Carrefour Polynésie</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>90104</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>French Polynesia</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Faaa</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Îles du Vent</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Immeuble Mana Nui</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>98 704</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>https://carrefour.pf</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>sages@sages.pf</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>+689 40 46 08 08</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr"/>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/carrefourpolynesie</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/carrefourpolynesie</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/carrefourtahiti2011</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>Jocelyn Bonneau</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr"/>
+      <c r="Z33" s="2" t="inlineStr"/>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jocelyn-bonneau-aa75341b0/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_French Polynesia.xlsx
+++ b/BWI/bestwine_output/bestwine_French Polynesia.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA33"/>
+  <dimension ref="A1:AA35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3851,6 +3851,208 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Carrefour Polynésie</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Carrefour Polynésie</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>90104</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>French Polynesia</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Faaa</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Îles du Vent</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Immeuble Mana Nui</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>98 704</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>https://carrefour.pf</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>sages@sages.pf</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>+689 40 46 08 08</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr"/>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/carrefourpolynesie</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/carrefourpolynesie</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/carrefourtahiti2011</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>Eric Corlier</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>Director Of Development</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr"/>
+      <c r="Z34" s="2" t="inlineStr"/>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/eric-corlier-b8644840/</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Carrefour Polynésie</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Carrefour Polynésie</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>90104</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>French Polynesia</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Faaa</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Îles du Vent</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Immeuble Mana Nui</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>98 704</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>https://carrefour.pf</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>sages@sages.pf</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>+689 40 46 08 08</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr"/>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/carrefourpolynesie</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/carrefourpolynesie</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/carrefourtahiti2011</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>Jocelyn Bonneau</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr"/>
+      <c r="Z35" s="2" t="inlineStr"/>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jocelyn-bonneau-aa75341b0/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_French Polynesia.xlsx
+++ b/BWI/bestwine_output/bestwine_French Polynesia.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA35"/>
+  <dimension ref="A1:AA37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -4053,6 +4053,208 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Carrefour Polynésie</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Carrefour Polynésie</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>90104</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>French Polynesia</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Faaa</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Îles du Vent</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Immeuble Mana Nui</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>98 704</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>https://carrefour.pf</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>sages@sages.pf</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>+689 40 46 08 08</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr"/>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/carrefourpolynesie</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/carrefourpolynesie</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/carrefourtahiti2011</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>Eric Corlier</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>Director Of Development</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr"/>
+      <c r="Z36" s="2" t="inlineStr"/>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/eric-corlier-b8644840/</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Carrefour Polynésie</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Carrefour Polynésie</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>90104</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>French Polynesia</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Faaa</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Îles du Vent</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Immeuble Mana Nui</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>98 704</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>https://carrefour.pf</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>sages@sages.pf</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>+689 40 46 08 08</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr"/>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/carrefourpolynesie</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/carrefourpolynesie</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/carrefourtahiti2011</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>Jocelyn Bonneau</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr"/>
+      <c r="Z37" s="2" t="inlineStr"/>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jocelyn-bonneau-aa75341b0/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_French Polynesia.xlsx
+++ b/BWI/bestwine_output/bestwine_French Polynesia.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA37"/>
+  <dimension ref="A1:AA39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -4255,6 +4255,208 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Carrefour Polynésie</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Carrefour Polynésie</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>90104</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>French Polynesia</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Faaa</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Îles du Vent</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Immeuble Mana Nui</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>98 704</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>https://carrefour.pf</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>sages@sages.pf</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>+689 40 46 08 08</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr"/>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/carrefourpolynesie</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/carrefourpolynesie</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/carrefourtahiti2011</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>Eric Corlier</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>Director Of Development</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr"/>
+      <c r="Z38" s="2" t="inlineStr"/>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/eric-corlier-b8644840/</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Carrefour Polynésie</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Carrefour Polynésie</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>90104</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>French Polynesia</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Faaa</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Îles du Vent</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Immeuble Mana Nui</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>98 704</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>https://carrefour.pf</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>sages@sages.pf</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>+689 40 46 08 08</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr"/>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/carrefourpolynesie</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/carrefourpolynesie</t>
+        </is>
+      </c>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/carrefourtahiti2011</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>Jocelyn Bonneau</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr"/>
+      <c r="Z39" s="2" t="inlineStr"/>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jocelyn-bonneau-aa75341b0/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
